--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jvz16\Proyectos\salon_agenda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42159345-7657-4050-A808-561DFDF1C89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CE112D-DCE6-4611-B23E-C21404910999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7156CD1D-D3BB-44C2-9761-0A4246B0D336}"/>
+    <workbookView xWindow="-21120" yWindow="2916" windowWidth="17280" windowHeight="9960" xr2:uid="{7156CD1D-D3BB-44C2-9761-0A4246B0D336}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>http://127.0.0.1:8000/reservar/</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>git commit -m "Background photo.py"</t>
+  </si>
+  <si>
+    <t>En admin: quitar "acciones recientes".</t>
   </si>
 </sst>
 </file>
@@ -500,8 +503,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>528754</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>148385</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>184580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -897,6 +900,12 @@
       </c>
     </row>
     <row r="5" spans="18:53">
+      <c r="R5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
       <c r="X5" t="s">
         <v>69</v>
       </c>
@@ -1090,7 +1099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="18:38" ht="31.5">
+    <row r="28" spans="18:38" ht="15" customHeight="1">
       <c r="X28" s="1" t="s">
         <v>17</v>
       </c>
@@ -1154,14 +1163,14 @@
       </c>
     </row>
     <row r="37" spans="18:38">
-      <c r="R37" t="s">
-        <v>6</v>
+      <c r="R37" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="AL37" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="18:38" ht="31.5">
+    <row r="38" spans="18:38" ht="15" customHeight="1">
       <c r="X38" s="1" t="s">
         <v>22</v>
       </c>
@@ -1171,7 +1180,7 @@
     </row>
     <row r="39" spans="18:38">
       <c r="R39" s="4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X39" s="2"/>
       <c r="AL39" t="s">
@@ -1184,6 +1193,9 @@
       </c>
     </row>
     <row r="41" spans="18:38">
+      <c r="R41" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="X41" s="2"/>
     </row>
     <row r="42" spans="18:38">
@@ -1310,10 +1322,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R39" r:id="rId1" xr:uid="{9C3E512A-7578-40DF-B9BE-12D578764726}"/>
+    <hyperlink ref="R41" r:id="rId1" xr:uid="{9C3E512A-7578-40DF-B9BE-12D578764726}"/>
+    <hyperlink ref="R37" r:id="rId2" xr:uid="{430B7A34-827B-4268-9EA3-1CF11552F7FD}"/>
+    <hyperlink ref="R39" r:id="rId3" xr:uid="{A2859F2B-1FF5-4E8F-AAB1-FA8588AAB133}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>